--- a/מסמך דרישות.xlsx
+++ b/מסמך דרישות.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leong\Desktop\Pet\second year\ניתוח מערכות מידע\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82B34E9-E874-470F-AF28-E564375B3078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA0794F-3F96-4022-B9B1-08C864BC6671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{25159B43-62BF-4F05-91E7-57A20698A675}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{25159B43-62BF-4F05-91E7-57A20698A675}"/>
   </bookViews>
   <sheets>
-    <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
-    <sheet name="גיליון2" sheetId="2" r:id="rId2"/>
+    <sheet name="גיליון2" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="55">
   <si>
     <t>מספר דרישה</t>
   </si>
@@ -48,82 +47,10 @@
     <t>מקור</t>
   </si>
   <si>
-    <t>סוג דרישה פונקציונלית</t>
-  </si>
-  <si>
-    <t>סוג דרישה  לא פונקציונלית</t>
-  </si>
-  <si>
-    <t>מסמך דרישות</t>
-  </si>
-  <si>
-    <t>לכל סניף אחראי משאבי אנוש במשרה חלקית</t>
-  </si>
-  <si>
-    <t>.עובדים יוכלו לגשת למערכת לעדכון פרטיהם האישיים בלבד</t>
-  </si>
-  <si>
-    <t>המערכת מאפשרת קליטת עובדים חדשים</t>
-  </si>
-  <si>
     <t>תפעולי</t>
   </si>
   <si>
-    <t>החברה עוסקת בתהליכי קליטת עובד,עדכון פרטי עובד ועזיבה</t>
-  </si>
-  <si>
-    <t>החברה עוסקת בתהליכי אפיון כללים</t>
-  </si>
-  <si>
-    <t>הסקה</t>
-  </si>
-  <si>
-    <t>ייעול ניהול העובד משלב קליטתו החברה ועד שלב עזיבתו .</t>
-  </si>
-  <si>
-    <t>מנהל משאבי אנוש בסניפים יועסק ב 1/4 משרה בלבד , לעומת 1/3 משרה היום .</t>
-  </si>
-  <si>
-    <t>מעדכוני פרטי עובד יתבצעו על ידי העובד עצמו.</t>
-  </si>
-  <si>
-    <t>האתר יוקם עד 5 חודשים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מנתח מערכות ותכנת ב- 1/2משרה כל אחד. </t>
-  </si>
-  <si>
-    <t>החברה מכנה להשקיע 35,000 פאונד עבור פיתוח התכנה.</t>
-  </si>
-  <si>
-    <t>ניהולי</t>
-  </si>
-  <si>
-    <t>חברה תצטרך לרכוש שרת , מדפסות, מערכת הפעלה ותוכנות נוספות</t>
-  </si>
-  <si>
     <t>חומרתי</t>
-  </si>
-  <si>
-    <t>המערכת תפותח בהתאם למחויבות בחוק הגנת הפרטיות ומאגרי מידע באנגליה</t>
-  </si>
-  <si>
-    <t>משתמש</t>
-  </si>
-  <si>
-    <t>הפונקציה</t>
-  </si>
-  <si>
-    <t>איכות</t>
-  </si>
-  <si>
-    <t>עובדים</t>
-  </si>
-  <si>
-    <t>מנהלים</t>
-  </si>
-  <si>
-    <t>משאבי אנוש</t>
   </si>
   <si>
     <t>המערכת תאפשר הרשמה למשתמשים חדשים</t>
@@ -306,7 +233,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -333,12 +260,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -356,7 +277,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -399,21 +320,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -422,35 +328,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -784,308 +678,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F055FF3B-545B-408E-8A21-FB5180655C39}">
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.09765625" customWidth="1"/>
-    <col min="4" max="4" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.296875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="10">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
-        <v>1.2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="10">
-        <v>2.1</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
-        <v>2.4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
-        <v>3.1</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>3.2</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
-        <v>3.3</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
-        <v>4.2</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11">
-        <v>4.5</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C55A2E9D-D4EB-4A23-81CB-8368FBA298FD}">
   <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -1098,20 +690,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>44</v>
+      <c r="D1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1119,15 +711,15 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1"/>
-      <c r="F2" s="14" t="s">
-        <v>39</v>
+      <c r="F2" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1135,15 +727,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E3" s="1"/>
-      <c r="F3" s="15" t="s">
-        <v>40</v>
+      <c r="F3" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1151,15 +743,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E4" s="1"/>
-      <c r="F4" s="15" t="s">
-        <v>41</v>
+      <c r="F4" s="7" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1167,15 +759,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="15" t="s">
-        <v>42</v>
+      <c r="F5" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1183,15 +775,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="15" t="s">
-        <v>43</v>
+      <c r="F6" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1199,82 +791,82 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="15"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="15"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="15"/>
+      <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E10" s="1"/>
-      <c r="F10" s="16"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="20"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="12"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="19" t="s">
-        <v>59</v>
+      <c r="F12" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1282,15 +874,15 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="19" t="s">
-        <v>60</v>
+      <c r="F13" s="11" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1298,15 +890,15 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E14" s="1"/>
-      <c r="F14" s="19" t="s">
-        <v>41</v>
+      <c r="F14" s="11" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1314,15 +906,15 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E15" s="1"/>
-      <c r="F15" s="19" t="s">
-        <v>39</v>
+      <c r="F15" s="11" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1330,15 +922,15 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="19" t="s">
-        <v>40</v>
+      <c r="F16" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1346,15 +938,15 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E17" s="1"/>
-      <c r="F17" s="19" t="s">
-        <v>42</v>
+      <c r="F17" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1362,15 +954,15 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E18" s="1"/>
-      <c r="F18" s="19" t="s">
-        <v>61</v>
+      <c r="F18" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1378,29 +970,29 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E19" s="1"/>
-      <c r="F19" s="19"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E20" s="1"/>
-      <c r="F20" s="19" t="s">
-        <v>63</v>
+      <c r="F20" s="11" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1408,15 +1000,15 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="2" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="E21" s="1"/>
-      <c r="F21" s="19" t="s">
-        <v>64</v>
+      <c r="F21" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1424,155 +1016,155 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="2" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="19" t="s">
-        <v>42</v>
+      <c r="F22" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="4"/>
+      <c r="B23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="3"/>
       <c r="D23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23" s="20"/>
+        <v>3</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G23" s="12"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="4"/>
+      <c r="B24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="3"/>
       <c r="D24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="20"/>
+        <v>46</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="12"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="21">
+      <c r="A25" s="13">
         <v>24</v>
       </c>
-      <c r="B25" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="22"/>
+      <c r="B25" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="14"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="9">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="19" t="s">
-        <v>61</v>
+        <v>3</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="9">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="4"/>
+        <v>47</v>
+      </c>
+      <c r="C27" s="3"/>
       <c r="D27" s="1"/>
       <c r="E27" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="9">
+      <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="C28" s="3"/>
       <c r="D28" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="19" t="s">
-        <v>76</v>
+      <c r="F28" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="9">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="4"/>
+        <v>44</v>
+      </c>
+      <c r="C29" s="3"/>
       <c r="D29" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="19" t="s">
-        <v>42</v>
+      <c r="F29" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="9">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="2" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="19" t="s">
-        <v>63</v>
+      <c r="F30" s="11" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="9">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>40</v>
+        <v>4</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1580,28 +1172,28 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F32" s="19"/>
+        <v>4</v>
+      </c>
+      <c r="F32" s="11"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" s="19"/>
+        <v>4</v>
+      </c>
+      <c r="F33" s="11"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
@@ -1609,7 +1201,7 @@
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
-      <c r="F34" s="19"/>
+      <c r="F34" s="11"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
@@ -1617,7 +1209,7 @@
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
-      <c r="F35" s="19"/>
+      <c r="F35" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/מסמך דרישות.xlsx
+++ b/מסמך דרישות.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leong\Desktop\Pet\second year\ניתוח מערכות מידע\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA0794F-3F96-4022-B9B1-08C864BC6671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5661ABD7-2DEF-42A0-9939-BF225D3FC9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{25159B43-62BF-4F05-91E7-57A20698A675}"/>
   </bookViews>
@@ -119,9 +119,6 @@
     <t>המערכת תאפשר ללקוחות לסנן אירועים לפי מיקום,רדיוס,סוג אירוע</t>
   </si>
   <si>
-    <t>המערכת תאפשר לרשימת החברים משתמשים אחרים</t>
-  </si>
-  <si>
     <t>המערכת תציג ללקוח את האירועים שלו בדף נפרד</t>
   </si>
   <si>
@@ -173,9 +170,6 @@
     <t xml:space="preserve">המערכת תסיר אירועים שכבר חלפו </t>
   </si>
   <si>
-    <t>מערכת תאפשר ללקוח להמנע מאנשים מסויימים שלא התחבר בעזרת כפתור</t>
-  </si>
-  <si>
     <t>תפועלי</t>
   </si>
   <si>
@@ -201,6 +195,12 @@
   </si>
   <si>
     <t xml:space="preserve">תפעול ואחזקה </t>
+  </si>
+  <si>
+    <t>המערכת תאפשר להוסיף לרשימת החברים משתמשים אחרים</t>
+  </si>
+  <si>
+    <t>מערכת תאפשר ללקוח לקבל התראות על אנשים מסוימים אשר משתתפים באירועים בעזרת כפתור</t>
   </si>
 </sst>
 </file>
@@ -866,7 +866,7 @@
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -882,7 +882,7 @@
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -890,7 +890,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="2" t="s">
@@ -938,7 +938,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="2" t="s">
@@ -954,7 +954,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="2" t="s">
@@ -962,7 +962,7 @@
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="2" t="s">
@@ -984,7 +984,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="2" t="s">
@@ -992,7 +992,7 @@
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1000,15 +1000,15 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1016,11 +1016,11 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="11" t="s">
@@ -1032,7 +1032,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="2" t="s">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G23" s="12"/>
     </row>
@@ -1049,11 +1049,11 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="11"/>
@@ -1064,7 +1064,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -1076,7 +1076,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="2" t="s">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1092,15 +1092,15 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="1"/>
       <c r="E27" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1108,7 +1108,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="2" t="s">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1124,7 +1124,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="2" t="s">
@@ -1140,7 +1140,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="2" t="s">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1156,7 +1156,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -1172,7 +1172,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -1186,7 +1186,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
